--- a/AAII_Financials/Quarterly/WDAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WDAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>WDAY</t>
   </si>
@@ -656,531 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2649000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2542000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2532000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2432000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2348000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2240000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2211000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2160000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2085000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1990000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1922000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1866000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1787000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1684000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1646300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1599100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1535800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1434700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1376100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1327300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1260400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1175000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1131700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1106000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1062000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1018400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>976300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>938100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>887800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>825100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>788600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>743200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>671700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>618600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>582500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>555400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>525300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>479900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>439600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>413500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>652000</v>
+      </c>
+      <c r="E9" s="3">
         <v>604000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>611000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>591000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>582000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>537000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>539000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>530000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>511000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>489000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>460000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>445000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>448000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>417000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>453500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>435800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>423100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>402800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>389800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>359700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>345500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>333100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>313000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>295200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>284300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>305600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>284800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>270900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>266300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>243200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>233700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>223000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>200200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>178000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>171000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>163600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>158200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>136700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>130200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>126900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1997000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1938000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1921000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1841000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1766000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1703000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1672000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1630000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1574000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1501000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1462000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1421000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1339000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1267000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1192800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1163300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1112700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1031900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>986300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>967600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>914900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>841900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>818700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>810800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>777700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>712800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>691500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>667200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>621500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>581900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>554900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>520200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>471500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>440600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>411500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>391800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>367100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>343200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>309400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>286600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,130 +1235,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E12" s="3">
         <v>705000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>691000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>666000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>660000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>663000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>674000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>647000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>649000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>656000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>635000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>619000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>610000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>615600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>565700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>547800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>541500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>537700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>455600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>444300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>441600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>439100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>420000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>418700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>443500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>422200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>401700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>378100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>347800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>337400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>318000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>292800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>263600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>253500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>239600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>221100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>196400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>191600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>185300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1467,53 +1483,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>96000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-16000</v>
       </c>
-      <c r="G14" s="3">
-        <v>3000</v>
-      </c>
       <c r="H14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="3">
         <v>167000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>87000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>16000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1553,8 +1572,8 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
@@ -1571,71 +1590,74 @@
       <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
         <v>600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>100</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E15" s="3">
         <v>92000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>97000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>85000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>81000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>84000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>91000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>79000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>75000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>72000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>71000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>70000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1711,8 +1733,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1752,252 +1777,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2336000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2204000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2227000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2168000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2099000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2035000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2061000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1995000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1973000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1918000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1843000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1778000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1751000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1735200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1625400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1569900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1507500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1477100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1303300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1261500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1213300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1205000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1120000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1078700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1162800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1122400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1048400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1010200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>948400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>908900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>925900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>760700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>689900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>664400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>635500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>606900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>540100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>528500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>519500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E18" s="3">
         <v>338000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>305000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>264000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>249000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>205000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>150000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>165000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>112000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>72000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>79000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>88000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-88900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-34100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-72800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-101000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-38300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-73300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-16700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-144400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-146100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-110300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-122400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-123300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-120300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-182700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-89000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-71300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-81900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-80100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-81600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-60200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-88900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-106000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2040,263 +2072,270 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-28000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
-        <v>1000</v>
-      </c>
       <c r="H20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>39500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>33800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>25700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>107100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>33300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>18700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>27200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>39000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>14500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>11900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>7800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>5300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>11600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E21" s="3">
         <v>429000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>430000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>352000</v>
       </c>
-      <c r="G21" s="3">
-        <v>329000</v>
-      </c>
       <c r="H21" s="3">
+        <v>327000</v>
+      </c>
+      <c r="I21" s="3">
         <v>290000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>243000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>246000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>191000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>150000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>153000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>161000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>109000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>99300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>56000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>136800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>191400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>67300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>64300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-66400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-37700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-25900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-40400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-43500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-86200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-27600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-18100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-35400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-36500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-39800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-21500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-44700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-64200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E22" s="3">
         <v>26000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>29000</v>
       </c>
       <c r="G22" s="3">
         <v>29000</v>
@@ -2305,22 +2344,22 @@
         <v>29000</v>
       </c>
       <c r="I22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="J22" s="3">
         <v>28000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>29000</v>
       </c>
       <c r="O22" s="3">
         <v>29000</v>
@@ -2329,22 +2368,22 @@
         <v>29000</v>
       </c>
       <c r="Q22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="R22" s="3">
         <v>28500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>29600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4100</v>
-      </c>
-      <c r="V22" s="3">
-        <v>4200</v>
       </c>
       <c r="W22" s="3">
         <v>4200</v>
@@ -2353,305 +2392,314 @@
         <v>4200</v>
       </c>
       <c r="Y22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z22" s="3">
         <v>15600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>17500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>18300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>18400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>12300</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>6800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>7000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E23" s="3">
         <v>355000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>264000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>338000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>304000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>103000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>120000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>227000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>168000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>123000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>138000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>129000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>82000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-77900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-22200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-66900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-93000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-83800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>45500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>101900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-47400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-68600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-22900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-28200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-155400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-129200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-114400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-122600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-116200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-105100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-156100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-87400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-75100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-88400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-83800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-80700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-61900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-91200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-109000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-305000</v>
+      </c>
+      <c r="E24" s="3">
         <v>133000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>119000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>86000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>76000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>36000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>16000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1050000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>47800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>52600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-10600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>10700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2772,252 +2820,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E26" s="3">
         <v>222000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>145000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>252000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>228000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>68000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>94000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>193000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>132000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>107000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1188000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>114000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>79000</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-125700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-74700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-64200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-102200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-73300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>43400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>105700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-158400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-128000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-99200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-85500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-110100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E27" s="3">
         <v>222000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>145000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>252000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>228000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>68000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>94000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>193000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>132000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>107000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1188000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>114000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>79000</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-125700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-74700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-64200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-102200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-73300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>43400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>105700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-158400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-128000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-99200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-85500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-110100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3138,8 +3195,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,17 +3284,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -3242,11 +3302,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>10100</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3260,8 +3320,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3382,8 +3445,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3504,252 +3570,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>28000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-39500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-33800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-25700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-107100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-33300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-27200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-19100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-14500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-11900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E33" s="3">
         <v>222000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>145000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>252000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>228000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>68000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>94000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>193000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>132000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>107000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1188000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>114000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>79000</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-125700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-74700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-64200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-102200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-73300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>43400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>105700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-158400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-128000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-89100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-85500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-110100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3870,257 +3945,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E35" s="3">
         <v>222000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>145000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>252000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>228000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>68000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>94000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>193000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>132000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>107000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1188000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>114000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>79000</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-125700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-74700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-64200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-102200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-73300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>43400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>105700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-158400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-128000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-89100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-85500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-110100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4163,8 +4247,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4207,374 +4292,384 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E41" s="3">
         <v>559000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1501000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2609000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1264000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>972000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1543000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1311000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1635000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1752000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2012000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1563900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1435700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1443700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1886300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1576000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2486500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2776300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1534300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1297300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1087100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>959400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1384200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1067000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1239700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1214200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>731100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>912700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>619500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>781800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>638600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>540400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1693700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1036000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1134400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1337000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>748600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>498900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>539900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>386600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2742000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3794000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3942000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4234000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6922000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6998000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6474000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5846000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5738000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5430000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5801000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5316000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5221400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4885300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4235100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3916100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3806400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3479000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2109900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2257700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2220900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2035200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2151500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1880800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1513800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1384800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1213400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1191800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1307000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1110100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1139900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1041700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1291400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>2329600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2133500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1874100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1349200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1616800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1456800</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1527200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1919000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1609000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2365000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1789000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1671000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1426000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2003000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1452000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1336000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1133000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1674000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1224800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1270900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1089300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1570100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1040500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1105300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>778100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1242500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>865000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>872800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>647200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1032500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>742700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>694300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>584200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>877600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>615500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>613400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>542800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>704700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>486000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>457500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>354200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>528200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>349300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>370600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>297900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>819600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>268900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4617,8 +4712,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4695,618 +4790,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>325000</v>
+        <v>346000</v>
       </c>
       <c r="E45" s="3">
         <v>325000</v>
       </c>
       <c r="F45" s="3">
+        <v>325000</v>
+      </c>
+      <c r="G45" s="3">
         <v>307000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>302000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>327000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>277000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>266000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>272000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>264000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>260400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>231200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>233000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>416700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>437700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>406400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>409800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>327400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>273700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>280400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>264100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>233900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>267700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>266400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>267100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>272500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>235300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>249100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>230400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>217500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>203100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>171400</v>
-      </c>
-      <c r="AJ45" s="3">
-        <v>160900</v>
       </c>
       <c r="AK45" s="3">
         <v>160900</v>
       </c>
       <c r="AL45" s="3">
+        <v>160900</v>
+      </c>
+      <c r="AM45" s="3">
         <v>133300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>117900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>120200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>117900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>111900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5969000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6592000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8429000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9175000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10407000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9963000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10545000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9078000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9200000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8874000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9939000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8574200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8381700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7873100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8108200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6970300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7804700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7443200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5214100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4693700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4461100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3905800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4802100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3958200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3714200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3450400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3094600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2955400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2789000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2665100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2700600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2271300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3614000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3880800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3957000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3693800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2586200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2533800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2524400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2294600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E47" s="3">
         <v>223000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>233000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>239000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>254000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>249000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>247000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>245000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>239000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>240000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>248000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>250300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>261500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>271100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>263500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>268500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>265600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>260600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>256800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>194600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>151900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>182200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>134100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>124300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>126500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>119600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>75000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>70800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>61300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>52900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>50500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>40200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>31600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>29200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>24300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>19200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>14500</v>
-      </c>
-      <c r="AO47" s="3">
-        <v>14000</v>
       </c>
       <c r="AP47" s="3">
         <v>14000</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>14000</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1827000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1812000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1853000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1840000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1495000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1575000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1598000</v>
       </c>
       <c r="K48" s="3">
         <v>1598000</v>
       </c>
       <c r="L48" s="3">
+        <v>1598000</v>
+      </c>
+      <c r="M48" s="3">
         <v>1561000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1523000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1472500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1484000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1472800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1450500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1487200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1519400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1438200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1370900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1389900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1411300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1436600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1386500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1392200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1282100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1247300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1227100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1218200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1214300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1165900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>796900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>735400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>678500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>611300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>546600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>487200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>438800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>404100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>365900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>334300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5857000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5893000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5931000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4836000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3821000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3842000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3864000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3888000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3614000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3633000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3105000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3122900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3130600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3152900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3166000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3187600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3209000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3231300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3253800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2815700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2759800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2780400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2086000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2097800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2112400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2128900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2145600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1669300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1686000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1692500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1711800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1721200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>222400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>199300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>204800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>192700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>197700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>202100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>209200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5427,8 +5540,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5549,130 +5665,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E52" s="3">
         <v>127000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>147000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>116000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>73000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>49000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>102000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>52000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>67300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>498000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>476100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>450900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>425700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>403000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>347000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>329600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>319000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>309700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>272500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>266300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>281300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>274100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>242000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>241500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>247700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>260900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>232200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>217700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>204800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>209800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>166700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>165300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>154300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>154700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5793,130 +5915,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15857000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16091000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18074000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17751000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17961000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17212000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17977000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16424000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16234000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15941000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16452000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13925900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13735300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13252800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13486200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12389800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13249600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12799100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10498500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9440900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9113800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8624000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8718400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7845000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7501500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7227500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6816400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6155600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5992200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5824200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5520700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5000300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4765100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4927800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4947400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4564700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3407100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3308700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3268300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2922600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5959,8 +6087,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6003,130 +6132,134 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E57" s="3">
         <v>116000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>142000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>103000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>92000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>108000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>87000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>76000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>78000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>79300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>88800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>113300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>153800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>75800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>60700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>123400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>55500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>47900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>53100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>75600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>54900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>57800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>35400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>57600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>35600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>32500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>35100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>29100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>28800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>32900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>30200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>21000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>35800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>39900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>28200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>26800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6134,609 +6267,624 @@
         <v>1129000</v>
       </c>
       <c r="E58" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="F58" s="3">
         <v>130000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>117000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>110000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>99000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>102000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>98000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>95000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>89000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>98300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>98800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>95000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>1149000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1148100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1222400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1212200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1202000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1191700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1103100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1091100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>37500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>266100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>244300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>241300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1233200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>235400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>232500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>229700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>570300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>341500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>336900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>332400</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AO58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP58" s="3" t="s">
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4446000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4404000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5093000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3932000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3914000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3861000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4490000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3460000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3565000</v>
       </c>
       <c r="L59" s="3">
         <v>3565000</v>
       </c>
       <c r="M59" s="3">
+        <v>3565000</v>
+      </c>
+      <c r="N59" s="3">
         <v>4072000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3213500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3326500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3242900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4474400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3647600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3648200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3509900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3789900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3014900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3019000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2970900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3104000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2479200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2457900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2469400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2667500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2214500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2168500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2172500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2169100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1797400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1654200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1596200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1696400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1376800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1304200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1261300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1258400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1069700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6573000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6535000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6378000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5017000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4945000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4821000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5548000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4422000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4513000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4428000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5055000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4029400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4182000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4044100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4628200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3723400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4857900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4781400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5067900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4275100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4274100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4210800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4282600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3625200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2553100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2771000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2969400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2491400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3434300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2443100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2430700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2055900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1913900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2196700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2058900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1749500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1676600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1289400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1285200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1098100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2643000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2676000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3691000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3676000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3666000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3295000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3263000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3261000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3266000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3249000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3207000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3177600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3170000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3159900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2975900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2975000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2974000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2973100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>617400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>636000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>654600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>673300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>691900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>701200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1752000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1508800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1018000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1006400</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>983500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>972300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>961100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>950100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>939200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1149800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1136500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>216000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>541400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>534400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>527500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E62" s="3">
         <v>127000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>129000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>109000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>113000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>112000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>48000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>296600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>282300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>289900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>263800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>278200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>314000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>317100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>334500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>466000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>440600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>357900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>345800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>342400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>338700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>347600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>352800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>159300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>150100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>125800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>134600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>158300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>138400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>144100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>157000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>172000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6857,8 +7005,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6979,8 +7130,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7101,130 +7255,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9397000</v>
+      </c>
+      <c r="E66" s="3">
         <v>9408000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10269000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8872000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8789000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8293000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8943000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7800000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7889000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7778000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8370000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7301000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7460800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7310900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7900700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6980700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8121700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8018300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5963400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5225100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5245900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5218600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5440600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4767000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4663000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4625500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4329800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3836500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3781900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3779400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3562300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3167200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2989800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3270500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3367100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3024400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2036700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1987900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1991700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1785100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7267,8 +7427,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7389,8 +7550,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7511,8 +7675,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7633,8 +7800,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7755,130 +7925,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-290000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-512000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-657000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-909000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1137000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1205000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1299000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1492000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1624000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1731000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2918800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3032500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3111200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3111300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2985600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2910900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2846800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2744600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2671300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2714700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2820500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2910000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2838300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2813900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2785900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2627400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2499400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2383700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2263000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2146300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2041800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1888000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-1801800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-1727900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-1638800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-1553200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-1470700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-1406900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-1415000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7999,8 +8175,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8121,8 +8300,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8243,130 +8425,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6460000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6683000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7805000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8879000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9172000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8919000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9034000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8624000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8345000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8163000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8082000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6624900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6274600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5941900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5585600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5409100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5127800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4780800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4535100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4215800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3868000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3405400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3277800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3078100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2838500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2602000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2486600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2319200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2210300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2044700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1958400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1833100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1775200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1657300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1580400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1540300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1370400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1320900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1276600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1137500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8487,257 +8675,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E81" s="3">
         <v>222000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>145000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>252000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>228000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>68000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>94000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>193000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>132000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>107000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1188000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>114000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>79000</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-125700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-74700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-64200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-102200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-73300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>43400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>105700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-46500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-24300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-158400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-128000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-115700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-120700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-116300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-104400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-86200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-74400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-89100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-85500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-82500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-64000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-88300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-110100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8780,130 +8977,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E83" s="3">
         <v>63000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>70000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>59000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>56000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>70900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>70700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>90000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>91900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>92700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>89800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>88800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>87100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>85400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>82500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>75100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>73900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>73200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>71500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>75100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>72200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>67800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>61200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>59600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>57600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>38700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>34600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>35000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>34000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>33400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>32600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>30500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9024,8 +9225,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9146,8 +9350,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9268,8 +9475,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9390,8 +9600,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9512,130 +9725,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E89" s="3">
         <v>696000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1278000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>588000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>616000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>457000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1112000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>406000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>571000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>372000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>996000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>451000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>425000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>277000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>694500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>408700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>114400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>439700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>615100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>384700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>198500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>452400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>553700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>293800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>157200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>263700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>297100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>258000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>100300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>209200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>250500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>114300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>57600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>184200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>126500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>144000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>15100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>180000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>109700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>71600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9678,130 +9897,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-60000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-86000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-81000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-60000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-77300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-59500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-168800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-58800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-81400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-87900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-34100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-55100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-37300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-39200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-44700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-27600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-23000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-60100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-107600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-174400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9922,8 +10145,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10044,130 +10270,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>946000</v>
+      </c>
+      <c r="E94" s="3">
         <v>97000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-844000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1687000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>13000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-523000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-727000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-451000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-345000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-258000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-481000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-172000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-385000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-713000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-380100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-168100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-487000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1470700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-439500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-166900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-139300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-861700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-299000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-462700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-202600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-277300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-541400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>32600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-320700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-67400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-202400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1268100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>912300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-284600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-362000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-595500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>201300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-222900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>18400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-99100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10210,8 +10442,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10254,8 +10487,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10332,8 +10565,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10454,8 +10690,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10576,8 +10815,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10698,138 +10940,144 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1366000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1733000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1544000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-925000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-349000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-501000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-154000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-281000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-348000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-367000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-67000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-150000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1149100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>83100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2277700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>62500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>66300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>60800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>70800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>499300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>62200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>58000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>49400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-311400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>32500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1039300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>32200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>25400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>10</v>
+      <c r="E101" s="3">
+        <v>1000</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>10</v>
@@ -10840,228 +11088,234 @@
       <c r="H101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>800</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-200</v>
       </c>
       <c r="AI101" s="3">
         <v>-200</v>
       </c>
       <c r="AJ101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-100</v>
       </c>
-      <c r="AO101" s="3">
-        <v>0</v>
-      </c>
       <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-941000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1109000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1349000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>281000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-566000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>231000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-326000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-122000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-253000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>448000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>128000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-439000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>307600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-909400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-289700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1246000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>237500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>210300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>125100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-420100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>316400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-174700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>26100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>485400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-182100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>292200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-162400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>144800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>97700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1151300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>658400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-98200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-202400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>587600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>249400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-40800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>153500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-22800</v>
       </c>
     </row>
